--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260713.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260713.xlsx
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>東和鋼鐵</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>15,639,000</t>
+          <t>10,225,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>東和鋼鐵</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>10,225,000</t>
+          <t>15,639,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>國產</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>24,248,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>國產</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>24,248,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
